--- a/Config/EnemyConfig.xlsx
+++ b/Config/EnemyConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\zizouqi\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24FEAEE3-8BE1-4460-BB64-CB2F36FB4117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12E804CB-A81F-4F34-80F7-5932FD20D187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9405" yWindow="7290" windowWidth="28800" windowHeight="12225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21705" yWindow="15360" windowWidth="21810" windowHeight="18945" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
   <si>
     <t>#</t>
   </si>
@@ -126,6 +126,14 @@
   </si>
   <si>
     <t>1,6,2|2,6,2|3,6,2|4,6,2|5,6,2|6,6,2|1,7,3|5,7,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全屏的 飞剑小兵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,6,5|2,6,5|3,6,5|4,6,5|5,6,5|6,6,5|1,7,5|2,7,5|3,7,5|4,7,5|5,7,5|6,7,5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -466,15 +474,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="14.5" customWidth="1"/>
     <col min="4" max="4" width="16.25" customWidth="1"/>
-    <col min="5" max="5" width="25.625" customWidth="1"/>
+    <col min="5" max="5" width="25.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -482,7 +490,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -496,7 +504,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -510,7 +518,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -527,12 +535,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>1</v>
       </c>
@@ -546,7 +554,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>2</v>
       </c>
@@ -558,6 +566,20 @@
       </c>
       <c r="E7" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8">
+        <v>3</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
